--- a/reports/Debug-purgatory-20260105/Week Total (Prior Year)_Payroll_history.xlsx
+++ b/reports/Debug-purgatory-20260105/Week Total (Prior Year)_Payroll_history.xlsx
@@ -19,6 +19,9 @@
     <t>department</t>
   </si>
   <si>
+    <t>D6215</t>
+  </si>
+  <si>
     <t>D1030</t>
   </si>
   <si>
@@ -40,7 +43,22 @@
     <t>D7010</t>
   </si>
   <si>
-    <t>D6215</t>
+    <t>D2200</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D4055</t>
+  </si>
+  <si>
+    <t>D5209</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D8020</t>
   </si>
   <si>
     <t>D5820</t>
@@ -50,24 +68,6 @@
   </si>
   <si>
     <t>D8050</t>
-  </si>
-  <si>
-    <t>D2200</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D4055</t>
-  </si>
-  <si>
-    <t>D5209</t>
-  </si>
-  <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>D8020</t>
   </si>
   <si>
     <t>D1000</t>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>5953.26</v>
+        <v>4585.84</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -536,7 +536,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>6189.67</v>
+        <v>5953.26</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -544,7 +544,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1597.96</v>
+        <v>6189.67</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -552,7 +552,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>43706.53</v>
+        <v>1597.96</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -560,7 +560,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>18995.44</v>
+        <v>43706.53</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -568,7 +568,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>934.36</v>
+        <v>18995.44</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -576,7 +576,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>2640.92</v>
+        <v>934.36</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -584,7 +584,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>4585.84</v>
+        <v>2640.92</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -592,7 +592,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>4049.57</v>
+        <v>2414.50</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -600,7 +600,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>14731.36</v>
+        <v>8982.61</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -608,7 +608,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>1576.96</v>
+        <v>4014.51</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -616,7 +616,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>2414.50</v>
+        <v>3009.84</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -624,7 +624,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>8982.61</v>
+        <v>15855.89</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -632,7 +632,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>4014.51</v>
+        <v>4308.91</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -640,7 +640,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>3009.84</v>
+        <v>4049.57</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -648,7 +648,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>15855.89</v>
+        <v>14731.36</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -656,7 +656,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>4308.91</v>
+        <v>1576.96</v>
       </c>
     </row>
     <row r="19" spans="1:2">
